--- a/data/insurance-glossary.xlsx
+++ b/data/insurance-glossary.xlsx
@@ -45086,7 +45086,7 @@
       </c>
       <c r="K722" s="16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L722" s="16" t="inlineStr">
